--- a/pbr_matchups_full.xlsx
+++ b/pbr_matchups_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9EE457-5C12-B141-A738-D734706215C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E020B8-F5C8-5947-9BF6-37F532740415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13520" yWindow="740" windowWidth="16720" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
     <sheet name="Billings Day 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="271">
   <si>
     <t>Bull Power</t>
   </si>
@@ -227,6 +227,9 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 94 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .183&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;32&lt;/span&gt; (16 for 51 - &lt;em&gt;31.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;137.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-690.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$49,517.31&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.31 to 89.31 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>Fade</t>
   </si>
   <si>
@@ -245,6 +248,9 @@
     <t>Right</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 126 for 328 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.41%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;10&lt;/span&gt; (26 for 67 - &lt;em&gt;38.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;392.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-435.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$125,660.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.96 to 91.96 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>Pass</t>
   </si>
   <si>
@@ -260,6 +266,9 @@
     <t>0.316 (6)</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 110 for 273 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.29%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.295&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;16&lt;/span&gt; (21 for 56 - &lt;em&gt;37.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;336.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-491.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$96,890.29&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>--</t>
   </si>
   <si>
@@ -275,6 +284,9 @@
     <t>0.234 (5)</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 154 for 515 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;29.9%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.250&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;38&lt;/span&gt; (21 for 70 - &lt;em&gt;30%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;86.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-741.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$85,787.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;-1 to 5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>27-6 (2)</t>
   </si>
   <si>
@@ -293,6 +305,9 @@
     <t>Rider 3.00%</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180 for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>7-0 (0)</t>
   </si>
   <si>
@@ -305,6 +320,9 @@
     <t>0.323 (7)</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 363 for 942 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.54%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.294&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (34 for 69 - &lt;em&gt;49.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-422.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$159,605.64&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.8 to 88.8 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 7 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>8-4 (1)</t>
   </si>
   <si>
@@ -341,6 +359,9 @@
     <t>Rider 40.00%</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 60 for 163 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;36.81%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.221&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;3&lt;/span&gt; (24 for 38 - &lt;em&gt;63.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;595.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-232)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$140,650.12&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 12 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;83.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 10 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;80%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>2-2 (2)</t>
   </si>
   <si>
@@ -905,653 +926,7 @@
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 258 for 576 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;44.79%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.372&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;6&lt;/span&gt; (36 for 66 - &lt;em&gt;54.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;488.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-339)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$252,397.78&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.74 to 89.74 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 16 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;56.25%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 13 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;46.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 94 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .183&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;32&lt;/span&gt; (16 for 51 - &lt;em&gt;31.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;137.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-690.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$49,517.31&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.31 to 89.31 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Kase Hitt is a left-handed, up-and-coming PBR bull rider from Dickson, Oklahoma, known for being tall and athletic with a gritty, keep-coming-back mindset. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Kase Hitt
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Dickson, Oklahoma, USA
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Oklahoma Wildcatters (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Left
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;21 years old, 6'2", ~150 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Earned his first Pendleton Whisky Velocity Tour victory at PBR Bangor in early 2026 with a three-ride comeback after bucking off his opening bull. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Logged a career-best UTB score with an 88.4‑point ride on Eyes On Me in the Championship Round at the 2026 PBR Pittsburgh Unleash The Beast event. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Won the PBR Stockyards Showcase in Fort Worth in 2024 with a walk‑off ride on Free Ride at Cowtown Coliseum, one of his early statement wins in the Challenger ranks. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Key closer for the Oklahoma Wildcatters in Teams competition, including clutch rides such as sealing wins at Thunder Days and other late‑game situations. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Tall, long‑levered left‑hander who uses his length and balance to stay over the front and finish strong, especially in rank short‑round matchups. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Built his name through smaller PBR and open bull ridings before breaking through on the Velocity Tour and earning UTB opportunities. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Recognized for mental toughness and the ability to bounce back after buckoffs, as seen in Bangor where he turned an early miss into a three‑ride surge for the win. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Rides with a straightforward, blue‑collar attitude that fits Oklahoma’s rodeo culture and the Wildcatters’ identity. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comes off as humble and soft‑spoken in interviews, but highly competitive in the chute, leaning on confidence in his feel and fundamentals more than flash. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Has already ridden through bumps and soreness at big events, building a reputation as a guy who keeps nodding his head even when he’s banged up. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Off the dirt, leans into the modern PBR lifestyle—social media, music, and team‑branding—while still coming across as a small‑town Oklahoma cowboy at heart. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 126 for 328 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.41%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;10&lt;/span&gt; (26 for 67 - &lt;em&gt;38.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;392.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-435.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$125,660.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.96 to 91.96 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Julio Cesar Marques is a right-handed Brazilian bull rider from Tatuí, São Paulo, a new‑generation star who quickly climbed into the very top tier of the PBR standings. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Julio Cesar Marques
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Tatuí, São Paulo, Brazil
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Kansas City Outlaws (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;22 years old, 5'6", ~145 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Broke through with his first Unleash The Beast event win at PBR Albany in late 2024, going a perfect 3‑for‑3 to claim the title and surge up the world standings. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Crowned “King of Deadwood” after dominating the historic Deadwood, South Dakota stop, stacking key rides in one of the tour’s most unique outdoor venues. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Logged multiple high‑mark UTB rides, including big scores on bulls like Lights Out, Tacky Jack, and Bayou Boy that helped push him into the No. 1 ranking battle. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Quickly became a consistent UTB contender, pushing into the top 5 and even No. 1 in the world race early in his career with strong finishes at major stops. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Classic young Brazilian technician with strong core position and timing, able to stay centered even when bulls are changing direction or speed. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Built his résumé through Brazil and U.S. Challenger/Velocity events before quickly adapting to UTB bulls and arenas, with almost no drop‑off under brighter lights. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Rides with a calm, composed look in the chute, then flips into an explosive, forward‑driving style once the gate opens. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Already viewed as one of the leaders of the new Brazilian wave, regularly mentioned as a future world‑title threat. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 p</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 110 for 273 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.29%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.295&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;16&lt;/span&gt; (21 for 56 - &lt;em&gt;37.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;336.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-491.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$96,890.29&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Kaiden “K‑Loud” Loud is a right-handed bull rider from Kaufman, Texas, a young UTB and Teams star known for big 90‑point moments and a loud, high‑energy presence in the arena. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Kaiden Loud
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Kaufman, Texas, USA
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Nashville Stampede (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;20 years old, athletic frame
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Dominated the high school ranks, including a Texas state title and youth bull riding championships, before jumping straight into the professional scene as a teenager. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Grabbed early national attention by winning the 2023 Tuff Hedeman Bull Riding in New Mexico at just 18 years old. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Selected by the Nashville Stampede in the second round of the 2023 PBR Teams Draft and quickly delivered clutch rides, including 90‑plus on bulls like Mike’s Motive and Ridin’ Salty. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Broke out individually at the 2024 PBR World Finals Eliminations in Fort Worth, winning the stage by going 3‑for‑4 and posting a 91.75‑point career‑best ride on Doze You Down. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      High‑energy, forward‑driving rider who uses quick reactions and strong hips to stay in the middle when bulls are firing hard and moving ahead. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comfortable under pressure in short‑round and World Finals‑type situations, with multiple rides over 88–90 points on big‑name bulls across UTB and Teams events. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Brings a showman streak—feeding off the crowd, celebrating big rides—and fits perfectly with Nashville’s “Broadway” personality on the Teams side. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Grew up in Texas rodeo culture and still trains and travels with other young guns like John Crimber, keeping a constant competitive environment around him. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Outgoing and media‑friendly, often featured in PBR content as “K‑Loud,” he leans into the spotlight without losing his workmanlike approach behind the scenes. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Close friends with fellow young star John Crimber; the two often practice together and push each other in and out of the arena. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Away from bull riding he stays active—shooting hoops, hanging around the barn, and keeping the same energetic, fun personality that shows up on TV. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 154 for 515 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;29.9%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.250&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;38&lt;/span&gt; (21 for 70 - &lt;em&gt;30%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;86.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-741.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$85,787.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;-1 to 5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Mauricio Gulla Moreira is a right-handed Brazilian bull rider from Gaviao Peixoto, São Paulo, a proven UTB and Teams veteran with a big-moment, high‑ceiling style. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Mauricio Gulla Moreira
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Gaviao Peixoto, São Paulo, Brazil
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;New York Mavericks (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Mid‑20s, compact and powerful build
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      4‑time PBR World Finals qualifier and 3‑time Teams World Finals qualifier, established as a top‑tier rider on both the premier series and the team side. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Multiple major wins and titles across PBR Brazil, Challenger, and Velocity‑type events, including an event championship at the historic PBR Stockyards Showcase in Fort Worth. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Produced big‑time UTB rides such as 88.75 on Tijuana Two Step at Madison Square Garden, 87.75 on Hell Right in Albany, and a 90‑point monster on Doze You Down during PBR Teams Outlaw Days. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Career headline stats: nearly 30% ride rate over more than 500 outs, a stack of mid‑to‑upper‑80s scores on rank bulls, and multiple 88‑90‑point rides that anchor both his individual and Teams résumé. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Classic Brazilian technician with strong posture, loose upper body and a lot of feel, letting bulls move around under him while he keeps his hips down and chest front. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comfortable in both big indoor arenas and smaller, rowdier outdoor setups; he has winning rides from New York City to Deadwood and Brazilian events back home. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Known for being tough and durable across long seasons, riding through soreness and staying in the mix of the world‑title conversation for multiple years. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Plays a veteran leader role on the New York Mavericks, often matched up with rank bulls in crucial Teams games. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comes across as calm and humble, quick to credit his faith and family, and lets his riding do most of the talking in big moments. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Has a strong fan following in both Brazil and the U.S., helped by his fun social‑media presence and highlight‑reel rides that regularly make PBR clips. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Off the dirt he leans into music, family, and a laid‑back Brazilian cowboy lifestyle, but inside the arena he rides like a guy who expects to win every matchup. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180 for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Bob Mitchell is a right-handed bull rider from Steelville, Missouri, a gritty, blue‑collar competitor who has turned himself into a steady threat on Velocity, UTB, and Teams. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Bob Mitchell
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Steelville, Missouri, USA
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;New York Mavericks (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Early 20s, 5'10", 160–170 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Broke out as a teenager by cracking the premier series and climbing into the Top 20 in the world at just 19 years old. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Logged key wins and rounds on the Pendleton Whisky Velocity Tour, including a Round 1 victory at PBR Grand Rapids and strong showings at Ride For Redemption in Fort Worth. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Career headline stats: about a 39% ride rate over more than 450 outs, a career average score in the low‑to‑mid‑80s, and a growing stack of 88‑plus rides at Velocity and UTB stops. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Fundamentally sound, compact rider who stays forward and aggressive, relying on strength and timing more than wild spur motion. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comfortable battling back after rough stretches, using smaller events and Velocity stops to rebuild confidence and momentum. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comes across as humble and straightforward, classic small‑town Missouri cowboy who doesn’t chase attention but rides with plenty of confidence. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt; for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 363 for 942 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.54%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.294&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (34 for 69 - &lt;em&gt;49.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-422.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$159,605.64&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.8 to 88.8 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 7 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Keyshawn Whitehorse is a right-handed bull rider from McCracken Spring, Utah, a seven‑time World Finals qualifier and cultural leader riding for the Navajo Nation. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Keyshawn Whitehorse
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;McCracken Spring, Utah, USA (Navajo Nation)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Arizona Ridge Riders (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;28 years old, 5'8", 155 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      2018 PBR Rookie of the Year and multiple‑time PBR World Finals qualifier, established as one of the most consistent riders of his era. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Has more than 20 career event wins across PBR levels, including multiple premier‑series titles and key Teams game‑winners. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Career headline stats: high‑30s ride rate over nearly 1,000 outs, dozens of 90‑point and high‑80 rides, and an average scoring profile in the mid‑80s when he covers. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Compact, technically polished rider with excellent balance and timing, rarely out of position and extremely good at finishing strong through the whistle. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Proudly represents the Navajo Nation, often talking about riding with purpose to honor his family, his people, and his faith. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 60 for 163 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;36.81%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.221&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;3&lt;/span&gt; (24 for 38 - &lt;em&gt;63.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;595.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-232)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$140,650.12&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 12 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;83.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 10 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;80%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Leandro Zampollo is a right-handed Brazilian bull rider from Pirassununga, São Paulo, one of the fastest‑rising young stars on the Unleash The Beast tour. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Leandro Zampollo
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Pirassununga, São Paulo, Brazil
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Florida Freedom (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Mid‑20s, 5'9", ~154 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Won the 2024 Hondo (Bridgeport) event and other Challenger/Velocity stops to punch his ticket onto UTB, where he quickly moved into the Top 30 in the world. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Claimed his first Unleash The Beast round win at Madison Square Garden in 2026, marked 88.4 points on UTZ BesTex Smokestack on Night 2 in New York. [web:243][web:246]
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Career headline stats: nearly 37% ride rate early in his UTB career, with an average score in the mid‑80s when he covers and multiple 88‑90‑point rides already on the board. [web:249]
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Smooth, forward‑driving Brazilian style with great timing around the corner, allowing him to stay centered and build points as bulls get stronger. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comes across as humble and appreciative of the opportunity, but rides with a chip‑on‑the‑shoulder intensity that fits his rapid rise from underdog to contender. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
+    <t>rr</t>
   </si>
 </sst>
 </file>
@@ -1982,6 +1357,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B688787-F410-204A-8FD8-EC4B8315D133}">
   <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="15" max="15" width="17.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -2009,25 +1387,25 @@
         <v>9</v>
       </c>
       <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" t="s">
         <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
       </c>
       <c r="P1" t="s">
         <v>16</v>
@@ -2071,35 +1449,35 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="P2">
-        <v>0</v>
+        <v>43.1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <f>IF(OR(P2="",R2=""),0,R2-P2)</f>
+        <v>45.35</v>
       </c>
       <c r="R2">
-        <f>P2+Q2</f>
-        <v>0</v>
+        <v>88.45</v>
       </c>
       <c r="T2" t="s">
         <v>19</v>
@@ -2131,36 +1509,35 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>263</v>
-      </c>
       <c r="P3">
-        <v>0</v>
+        <v>42.7</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R44" si="0">P3+Q3</f>
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2171,10 +1548,10 @@
         <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -2187,36 +1564,37 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="P4">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <f t="shared" ref="Q3:Q44" ca="1" si="0">IF(OR(P4="",R4=""),0,R4-P4)</f>
+        <v>45.4</v>
       </c>
       <c r="R4">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f ca="1">P4+Q4</f>
+        <v>83.15</v>
       </c>
       <c r="T4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2227,10 +1605,10 @@
         <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -2243,36 +1621,35 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>265</v>
+        <v>50</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>44.2</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
       <c r="R5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2283,14 +1660,14 @@
         <v>31</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -2299,36 +1676,35 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>266</v>
+        <v>56</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>44.2</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2339,14 +1715,14 @@
         <v>67.349999999999994</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
@@ -2355,35 +1731,34 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>26</v>
+        <v>61</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>267</v>
+        <v>63</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>41.1</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>83.85</v>
       </c>
       <c r="T7" t="s">
         <v>19</v>
@@ -2397,14 +1772,14 @@
         <v>74.319999999999993</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>23</v>
@@ -2413,36 +1788,36 @@
         <v>2</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" s="3"/>
+        <v>67</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>268</v>
+        <v>68</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>44.15</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="R8:R44" si="1">P8+Q8</f>
+        <v>44.15</v>
       </c>
       <c r="T8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2453,14 +1828,14 @@
         <v>67.02</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -2469,38 +1844,38 @@
         <v>2</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>26</v>
+        <v>73</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>42.9</v>
       </c>
       <c r="T9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2511,14 +1886,14 @@
         <v>72.430000000000007</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>23</v>
@@ -2527,25 +1902,25 @@
         <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>26</v>
+        <v>79</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>269</v>
+        <v>81</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -2554,7 +1929,6 @@
         <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T10" t="s">
@@ -2569,14 +1943,14 @@
         <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>23</v>
@@ -2585,36 +1959,36 @@
         <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>43.55</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>45.960000000000008</v>
       </c>
       <c r="R11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>89.51</v>
       </c>
       <c r="T11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2625,16 +1999,16 @@
         <v>41.22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E12" s="1">
         <v>10266759</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>23</v>
@@ -2643,33 +2017,32 @@
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P12" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>270</v>
+      </c>
+      <c r="R12" t="s">
+        <v>270</v>
       </c>
       <c r="T12" t="s">
         <v>19</v>
@@ -2683,16 +2056,16 @@
         <v>78.040000000000006</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E13" s="1">
         <v>10231236</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>23</v>
@@ -2701,38 +2074,38 @@
         <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>26</v>
+        <v>97</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>43.15</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>43.000000000000007</v>
       </c>
       <c r="R13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>86.15</v>
       </c>
       <c r="T13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2746,13 +2119,13 @@
         <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E14" s="1">
         <v>10259466</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>23</v>
@@ -2761,36 +2134,36 @@
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M14" s="6"/>
+        <v>103</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-43</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2801,14 +2174,14 @@
         <v>59.91</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>23</v>
@@ -2817,38 +2190,38 @@
         <v>3</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>26</v>
+        <v>109</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R15">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2859,16 +2232,16 @@
         <v>71.7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E16" s="1">
         <v>10257887</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>23</v>
@@ -2877,36 +2250,36 @@
         <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M16" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="P16">
         <v>0</v>
       </c>
       <c r="Q16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R16">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2917,14 +2290,14 @@
         <v>77.53</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>23</v>
@@ -2933,36 +2306,36 @@
         <v>3</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R17">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2973,14 +2346,14 @@
         <v>69.67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>23</v>
@@ -2989,38 +2362,38 @@
         <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>26</v>
+        <v>126</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
       <c r="Q18">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R18">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3031,14 +2404,14 @@
         <v>77.599999999999994</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
@@ -3047,38 +2420,38 @@
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>26</v>
+        <v>132</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="P19">
         <v>0</v>
       </c>
       <c r="Q19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R19">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3089,14 +2462,14 @@
         <v>31</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>23</v>
@@ -3105,32 +2478,32 @@
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R20">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T20" t="s">
@@ -3145,16 +2518,16 @@
         <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E21" s="1">
         <v>10259151</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>23</v>
@@ -3163,32 +2536,32 @@
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="6"/>
+        <v>142</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="P21">
         <v>0</v>
       </c>
       <c r="Q21">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R21">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T21" t="s">
@@ -3203,14 +2576,14 @@
         <v>31</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>23</v>
@@ -3219,32 +2592,32 @@
         <v>4</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M22" s="6"/>
+        <v>147</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R22">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T22" t="s">
@@ -3259,16 +2632,16 @@
         <v>64.7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E23" s="1">
         <v>10269156</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>23</v>
@@ -3277,32 +2650,32 @@
         <v>4</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M23" s="3"/>
+        <v>152</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R23">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T23" t="s">
@@ -3317,14 +2690,14 @@
         <v>64.67</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>23</v>
@@ -3333,38 +2706,38 @@
         <v>4</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>26</v>
+        <v>158</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R24">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3375,14 +2748,14 @@
         <v>31</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>23</v>
@@ -3391,36 +2764,36 @@
         <v>4</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R25">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3431,16 +2804,16 @@
         <v>56.01</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E26" s="1">
         <v>10239182</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>23</v>
@@ -3449,34 +2822,34 @@
         <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>26</v>
+        <v>170</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>164</v>
+        <v>99</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R26">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T26" t="s">
@@ -3491,16 +2864,16 @@
         <v>31</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E27" s="1">
         <v>10262517</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>23</v>
@@ -3509,36 +2882,36 @@
         <v>5</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M27" s="6"/>
+        <v>175</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R27">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3549,14 +2922,14 @@
         <v>86.05</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>23</v>
@@ -3565,38 +2938,38 @@
         <v>5</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>26</v>
+        <v>181</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R28">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3607,14 +2980,14 @@
         <v>70.64</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>23</v>
@@ -3623,38 +2996,38 @@
         <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>26</v>
+        <v>188</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>27</v>
+        <v>189</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R29">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3665,14 +3038,14 @@
         <v>31</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>23</v>
@@ -3681,36 +3054,36 @@
         <v>5</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="P30">
         <v>0</v>
       </c>
       <c r="Q30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3721,14 +3094,14 @@
         <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>23</v>
@@ -3737,36 +3110,36 @@
         <v>6</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="P31">
         <v>0</v>
       </c>
       <c r="Q31">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R31">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3777,16 +3150,16 @@
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E32" s="1">
         <v>10266753</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>23</v>
@@ -3795,32 +3168,32 @@
         <v>6</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M32" s="6"/>
+        <v>203</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="6"/>
+      <c r="M32" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R32">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T32" t="s">
@@ -3835,16 +3208,16 @@
         <v>89.52</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E33" s="1">
         <v>10203017</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>23</v>
@@ -3853,38 +3226,38 @@
         <v>6</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>26</v>
+        <v>208</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="P33">
         <v>0</v>
       </c>
       <c r="Q33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R33">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3895,10 +3268,10 @@
         <v>74.709999999999994</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
@@ -3911,38 +3284,38 @@
         <v>6</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>26</v>
+        <v>214</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>208</v>
+        <v>99</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R34">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3953,14 +3326,14 @@
         <v>31</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>23</v>
@@ -3969,38 +3342,38 @@
         <v>7</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>26</v>
+        <v>220</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>208</v>
+        <v>99</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="P35">
         <v>0</v>
       </c>
       <c r="Q35">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R35">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4011,14 +3384,14 @@
         <v>31</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>23</v>
@@ -4027,36 +3400,36 @@
         <v>7</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M36" s="6"/>
+        <v>223</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="6"/>
+      <c r="M36" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="P36">
         <v>0</v>
       </c>
       <c r="Q36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R36">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4067,16 +3440,16 @@
         <v>81.430000000000007</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E37" s="1">
         <v>10243244</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>23</v>
@@ -4085,38 +3458,38 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>26</v>
+        <v>228</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>42</v>
+        <v>229</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="P37">
         <v>0</v>
       </c>
       <c r="Q37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R37">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4127,16 +3500,16 @@
         <v>31</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E38" s="1">
         <v>10268368</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>23</v>
@@ -4145,36 +3518,36 @@
         <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M38" s="6"/>
+        <v>233</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="6"/>
+      <c r="M38" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R38">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4185,16 +3558,16 @@
         <v>57.96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E39" s="1">
         <v>10239944</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>23</v>
@@ -4203,38 +3576,38 @@
         <v>8</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>26</v>
+        <v>239</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>233</v>
+        <v>29</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="P39">
         <v>0</v>
       </c>
       <c r="Q39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R39">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4245,14 +3618,14 @@
         <v>70.33</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>23</v>
@@ -4261,32 +3634,32 @@
         <v>8</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="P40">
         <v>0</v>
       </c>
       <c r="Q40">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R40">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T40" t="s">
@@ -4301,16 +3674,16 @@
         <v>86.7</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E41" s="1">
         <v>10222050</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>23</v>
@@ -4319,38 +3692,38 @@
         <v>9</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>26</v>
+        <v>251</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>27</v>
+        <v>252</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>245</v>
+        <v>99</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="P41">
         <v>0</v>
       </c>
       <c r="Q41">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R41">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4364,13 +3737,13 @@
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E42" s="1">
         <v>10274756</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>23</v>
@@ -4379,36 +3752,36 @@
         <v>9</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="P42">
         <v>0</v>
       </c>
       <c r="Q42">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R42">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4419,14 +3792,14 @@
         <v>52.8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>23</v>
@@ -4435,34 +3808,34 @@
         <v>9</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>26</v>
+        <v>261</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>255</v>
+        <v>99</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="P43">
         <v>0</v>
       </c>
       <c r="Q43">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R43">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T43" t="s">
@@ -4477,16 +3850,16 @@
         <v>65.78</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E44" s="1">
         <v>10258756</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>23</v>
@@ -4495,34 +3868,34 @@
         <v>9</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>26</v>
+        <v>267</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R44">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T44" t="s">
@@ -4531,49 +3904,49 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Jess+Lockwood" xr:uid="{F970B9C6-9BCD-5E46-AA4F-71F0EACB3924}"/>
-    <hyperlink ref="K3" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Kase+Hitt" xr:uid="{F506C8E8-40E1-964F-B9DA-D7FE929F019A}"/>
-    <hyperlink ref="K4" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Julio+Cesar+Marques" xr:uid="{053518A0-6349-4744-95DE-41EFA4861A41}"/>
-    <hyperlink ref="K5" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Kaiden+Loud" xr:uid="{8C7DDD88-3D1A-C94E-923A-DA0DBC8146AD}"/>
-    <hyperlink ref="K6" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{FD7D6547-2C8C-2840-A167-738CAB9A832C}"/>
-    <hyperlink ref="K7" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=48948&amp;guy=Bob+Mitchell" xr:uid="{F0059777-5DFE-F946-AC6B-1EDDB6C3D6AF}"/>
-    <hyperlink ref="K8" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Keyshawn+Whitehorse" xr:uid="{B26D7B4B-123C-0149-ADFC-45AB02B58CFD}"/>
-    <hyperlink ref="K9" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=53968&amp;guy=Manoelito+de+Souza+Junior" xr:uid="{569F14A1-459F-2244-90DC-CB697A4D3339}"/>
-    <hyperlink ref="K10" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=53970&amp;guy=Leandro+Zampollo" xr:uid="{1F2BFB5A-99B7-9846-A2AC-C3775B994DBD}"/>
-    <hyperlink ref="K11" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56046&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{6DB243E9-BFED-B842-B9FC-F6B37C950BA1}"/>
-    <hyperlink ref="K12" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=54711&amp;guy=Alex+Cerqueira" xr:uid="{6008F3BA-B37C-924B-8487-8673B80C5062}"/>
-    <hyperlink ref="K13" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=47944&amp;guy=Luciano+De+Castro" xr:uid="{9267FA7D-248E-B34C-8C38-7BE0A78E8AEA}"/>
-    <hyperlink ref="K14" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=54869&amp;guy=Maverick+Smith" xr:uid="{D678A161-F7D7-2F41-B2E8-5D745A686CC6}"/>
-    <hyperlink ref="K15" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=52181&amp;guy=Hudson+Bolton" xr:uid="{AD073728-5785-1A4F-A08B-4B96F315C8A4}"/>
-    <hyperlink ref="K16" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=52572&amp;guy=Alex+Junior+da+Silva" xr:uid="{7E120FEA-998C-D94A-9898-25668BC671E8}"/>
-    <hyperlink ref="K17" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=55061&amp;guy=Bruno+Carvalho" xr:uid="{0556D485-6D01-CC4C-87EB-623E88F2E932}"/>
-    <hyperlink ref="K18" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=54896&amp;guy=Mason+Taylor" xr:uid="{4D30E132-8232-7C42-9CD6-B9669F98DF66}"/>
-    <hyperlink ref="K19" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=52731&amp;guy=Marco+Rizzo" xr:uid="{1266D028-E5E7-0146-B7F2-D84A3EB2D983}"/>
-    <hyperlink ref="K20" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=56541&amp;guy=John+Crimber" xr:uid="{B409839B-8FC2-804B-92CB-C6EB4D712DA3}"/>
-    <hyperlink ref="K21" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=55423&amp;guy=Eduardo+Aparecido" xr:uid="{581E78AC-8306-9D44-B916-342AC1D9626F}"/>
-    <hyperlink ref="K22" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=55889&amp;guy=Brady+Fielder" xr:uid="{325C0132-97EC-AB4C-9652-5EB81533072B}"/>
-    <hyperlink ref="K23" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=55691&amp;guy=Claudio+Montanha+Jr." xr:uid="{7CD20EF3-9BDD-5748-87FB-A8B4A3E49BDB}"/>
-    <hyperlink ref="K24" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=50890&amp;guy=Trace+Redd" xr:uid="{2C05EFFD-59C7-DC42-AE87-3CEB6B55C7DD}"/>
-    <hyperlink ref="K25" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=56045&amp;guy=Daniel+Keeping" xr:uid="{469A118B-00C6-4B49-B5C6-A3C6C9B15ACC}"/>
-    <hyperlink ref="K26" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=52122&amp;guy=Jose+Vitor+Leme" xr:uid="{3C3E0CC1-BD10-3B44-ADAF-07E4338402BA}"/>
-    <hyperlink ref="K27" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Cort+McFadden" xr:uid="{129071F9-1177-4340-9B59-0E2D000E9C69}"/>
-    <hyperlink ref="K28" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=45407&amp;guy=Jadon+Hayes" xr:uid="{963E5A5A-6D28-2349-935F-133EDC8262EA}"/>
-    <hyperlink ref="K29" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=48463&amp;guy=Joao+Ricardo+Vieira" xr:uid="{9ACEEFE7-F7D3-7E4A-9BF5-24143405AFA1}"/>
-    <hyperlink ref="K30" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=53635&amp;guy=Macaulie+Leather" xr:uid="{B697B491-58DB-4B4B-8562-9AB358049F51}"/>
-    <hyperlink ref="K31" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56345&amp;guy=Natanael+Serra+Aires" xr:uid="{0BCBF768-93D3-8F43-8AD5-206A7FB3B833}"/>
-    <hyperlink ref="K32" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=55084&amp;guy=Sage+Kimzey" xr:uid="{D66640D7-CE04-A640-86B0-643111985C5C}"/>
-    <hyperlink ref="K33" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=43263&amp;guy=Eric+Henrique+Domingos" xr:uid="{716167A1-FB1B-D243-A41C-5B4ADE29A6E6}"/>
-    <hyperlink ref="K34" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=50683&amp;guy=Kaique+Pacheco" xr:uid="{180B9CC1-DC3C-A947-96FF-6EB1A3EB77CB}"/>
-    <hyperlink ref="K35" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=53634&amp;guy=Marcelo+De+Souza+Dias+Junior" xr:uid="{0BB40081-B139-2F4C-B0A3-9745E426BEAF}"/>
-    <hyperlink ref="K36" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=55693&amp;guy=Callum+Miller" xr:uid="{2A7095C3-9A96-904C-8825-FDD5D393F760}"/>
-    <hyperlink ref="K37" r:id="rId36" display="https://probullstats.com/loggers/matchup.php?bull=52004&amp;guy=Bruno+Roberto" xr:uid="{2A512A64-74CA-7246-911B-43D2ADA4C788}"/>
-    <hyperlink ref="K38" r:id="rId37" display="https://probullstats.com/loggers/matchup.php?bull=56543&amp;guy=Lucas+Divino" xr:uid="{74303718-CC19-714D-B767-E9BF6F270DFC}"/>
-    <hyperlink ref="K39" r:id="rId38" display="https://probullstats.com/loggers/matchup.php?bull=47812&amp;guy=Andy+Guzman" xr:uid="{BCB8E763-7EFC-C64A-A714-03EAC79C3956}"/>
-    <hyperlink ref="K40" r:id="rId39" display="https://probullstats.com/loggers/matchup.php?bull=52618&amp;guy=Dener+Barbosa" xr:uid="{094DB341-E704-864E-ABEE-F20088B176D7}"/>
-    <hyperlink ref="K41" r:id="rId40" display="https://probullstats.com/loggers/matchup.php?bull=47325&amp;guy=Koltin+Hevalow" xr:uid="{0A517EBE-BEF9-0B49-A775-5E7D09C557BE}"/>
-    <hyperlink ref="K42" r:id="rId41" display="https://probullstats.com/loggers/matchup.php?bull=56319&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{7DAB5BE5-3791-D249-A50F-F3D91CAD6DA7}"/>
-    <hyperlink ref="K43" r:id="rId42" display="https://probullstats.com/loggers/matchup.php?bull=52178&amp;guy=Cassio+Dias" xr:uid="{3D7C6384-160B-8A48-A29D-CB20A28B4E76}"/>
-    <hyperlink ref="K44" r:id="rId43" display="https://probullstats.com/loggers/matchup.php?bull=54035&amp;guy=Dalton+Kasel" xr:uid="{0EDD66C9-F792-EC45-A24C-1F3BD6F40636}"/>
+    <hyperlink ref="J2" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Jess+Lockwood" xr:uid="{F970B9C6-9BCD-5E46-AA4F-71F0EACB3924}"/>
+    <hyperlink ref="J3" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Kase+Hitt" xr:uid="{F506C8E8-40E1-964F-B9DA-D7FE929F019A}"/>
+    <hyperlink ref="J4" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Julio+Cesar+Marques" xr:uid="{053518A0-6349-4744-95DE-41EFA4861A41}"/>
+    <hyperlink ref="J5" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Kaiden+Loud" xr:uid="{8C7DDD88-3D1A-C94E-923A-DA0DBC8146AD}"/>
+    <hyperlink ref="J6" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{FD7D6547-2C8C-2840-A167-738CAB9A832C}"/>
+    <hyperlink ref="J7" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=48948&amp;guy=Bob+Mitchell" xr:uid="{F0059777-5DFE-F946-AC6B-1EDDB6C3D6AF}"/>
+    <hyperlink ref="J8" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Keyshawn+Whitehorse" xr:uid="{B26D7B4B-123C-0149-ADFC-45AB02B58CFD}"/>
+    <hyperlink ref="J9" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=53968&amp;guy=Manoelito+de+Souza+Junior" xr:uid="{569F14A1-459F-2244-90DC-CB697A4D3339}"/>
+    <hyperlink ref="J10" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=53970&amp;guy=Leandro+Zampollo" xr:uid="{1F2BFB5A-99B7-9846-A2AC-C3775B994DBD}"/>
+    <hyperlink ref="J11" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56046&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{6DB243E9-BFED-B842-B9FC-F6B37C950BA1}"/>
+    <hyperlink ref="J12" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=54711&amp;guy=Alex+Cerqueira" xr:uid="{6008F3BA-B37C-924B-8487-8673B80C5062}"/>
+    <hyperlink ref="J13" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=47944&amp;guy=Luciano+De+Castro" xr:uid="{9267FA7D-248E-B34C-8C38-7BE0A78E8AEA}"/>
+    <hyperlink ref="J14" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=54869&amp;guy=Maverick+Smith" xr:uid="{D678A161-F7D7-2F41-B2E8-5D745A686CC6}"/>
+    <hyperlink ref="J15" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=52181&amp;guy=Hudson+Bolton" xr:uid="{AD073728-5785-1A4F-A08B-4B96F315C8A4}"/>
+    <hyperlink ref="J16" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=52572&amp;guy=Alex+Junior+da+Silva" xr:uid="{7E120FEA-998C-D94A-9898-25668BC671E8}"/>
+    <hyperlink ref="J17" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=55061&amp;guy=Bruno+Carvalho" xr:uid="{0556D485-6D01-CC4C-87EB-623E88F2E932}"/>
+    <hyperlink ref="J18" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=54896&amp;guy=Mason+Taylor" xr:uid="{4D30E132-8232-7C42-9CD6-B9669F98DF66}"/>
+    <hyperlink ref="J19" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=52731&amp;guy=Marco+Rizzo" xr:uid="{1266D028-E5E7-0146-B7F2-D84A3EB2D983}"/>
+    <hyperlink ref="J20" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=56541&amp;guy=John+Crimber" xr:uid="{B409839B-8FC2-804B-92CB-C6EB4D712DA3}"/>
+    <hyperlink ref="J21" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=55423&amp;guy=Eduardo+Aparecido" xr:uid="{581E78AC-8306-9D44-B916-342AC1D9626F}"/>
+    <hyperlink ref="J22" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=55889&amp;guy=Brady+Fielder" xr:uid="{325C0132-97EC-AB4C-9652-5EB81533072B}"/>
+    <hyperlink ref="J23" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=55691&amp;guy=Claudio+Montanha+Jr." xr:uid="{7CD20EF3-9BDD-5748-87FB-A8B4A3E49BDB}"/>
+    <hyperlink ref="J24" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=50890&amp;guy=Trace+Redd" xr:uid="{2C05EFFD-59C7-DC42-AE87-3CEB6B55C7DD}"/>
+    <hyperlink ref="J25" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=56045&amp;guy=Daniel+Keeping" xr:uid="{469A118B-00C6-4B49-B5C6-A3C6C9B15ACC}"/>
+    <hyperlink ref="J26" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=52122&amp;guy=Jose+Vitor+Leme" xr:uid="{3C3E0CC1-BD10-3B44-ADAF-07E4338402BA}"/>
+    <hyperlink ref="J27" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Cort+McFadden" xr:uid="{129071F9-1177-4340-9B59-0E2D000E9C69}"/>
+    <hyperlink ref="J28" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=45407&amp;guy=Jadon+Hayes" xr:uid="{963E5A5A-6D28-2349-935F-133EDC8262EA}"/>
+    <hyperlink ref="J29" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=48463&amp;guy=Joao+Ricardo+Vieira" xr:uid="{9ACEEFE7-F7D3-7E4A-9BF5-24143405AFA1}"/>
+    <hyperlink ref="J30" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=53635&amp;guy=Macaulie+Leather" xr:uid="{B697B491-58DB-4B4B-8562-9AB358049F51}"/>
+    <hyperlink ref="J31" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56345&amp;guy=Natanael+Serra+Aires" xr:uid="{0BCBF768-93D3-8F43-8AD5-206A7FB3B833}"/>
+    <hyperlink ref="J32" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=55084&amp;guy=Sage+Kimzey" xr:uid="{D66640D7-CE04-A640-86B0-643111985C5C}"/>
+    <hyperlink ref="J33" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=43263&amp;guy=Eric+Henrique+Domingos" xr:uid="{716167A1-FB1B-D243-A41C-5B4ADE29A6E6}"/>
+    <hyperlink ref="J34" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=50683&amp;guy=Kaique+Pacheco" xr:uid="{180B9CC1-DC3C-A947-96FF-6EB1A3EB77CB}"/>
+    <hyperlink ref="J35" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=53634&amp;guy=Marcelo+De+Souza+Dias+Junior" xr:uid="{0BB40081-B139-2F4C-B0A3-9745E426BEAF}"/>
+    <hyperlink ref="J36" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=55693&amp;guy=Callum+Miller" xr:uid="{2A7095C3-9A96-904C-8825-FDD5D393F760}"/>
+    <hyperlink ref="J37" r:id="rId36" display="https://probullstats.com/loggers/matchup.php?bull=52004&amp;guy=Bruno+Roberto" xr:uid="{2A512A64-74CA-7246-911B-43D2ADA4C788}"/>
+    <hyperlink ref="J38" r:id="rId37" display="https://probullstats.com/loggers/matchup.php?bull=56543&amp;guy=Lucas+Divino" xr:uid="{74303718-CC19-714D-B767-E9BF6F270DFC}"/>
+    <hyperlink ref="J39" r:id="rId38" display="https://probullstats.com/loggers/matchup.php?bull=47812&amp;guy=Andy+Guzman" xr:uid="{BCB8E763-7EFC-C64A-A714-03EAC79C3956}"/>
+    <hyperlink ref="J40" r:id="rId39" display="https://probullstats.com/loggers/matchup.php?bull=52618&amp;guy=Dener+Barbosa" xr:uid="{094DB341-E704-864E-ABEE-F20088B176D7}"/>
+    <hyperlink ref="J41" r:id="rId40" display="https://probullstats.com/loggers/matchup.php?bull=47325&amp;guy=Koltin+Hevalow" xr:uid="{0A517EBE-BEF9-0B49-A775-5E7D09C557BE}"/>
+    <hyperlink ref="J42" r:id="rId41" display="https://probullstats.com/loggers/matchup.php?bull=56319&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{7DAB5BE5-3791-D249-A50F-F3D91CAD6DA7}"/>
+    <hyperlink ref="J43" r:id="rId42" display="https://probullstats.com/loggers/matchup.php?bull=52178&amp;guy=Cassio+Dias" xr:uid="{3D7C6384-160B-8A48-A29D-CB20A28B4E76}"/>
+    <hyperlink ref="J44" r:id="rId43" display="https://probullstats.com/loggers/matchup.php?bull=54035&amp;guy=Dalton+Kasel" xr:uid="{0EDD66C9-F792-EC45-A24C-1F3BD6F40636}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pbr_matchups_full.xlsx
+++ b/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E020B8-F5C8-5947-9BF6-37F532740415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D2FA8B-5119-FE4A-AACF-CB09959EC24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="277">
   <si>
     <t>Bull Power</t>
   </si>
@@ -926,14 +926,32 @@
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 258 for 576 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;44.79%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.372&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;6&lt;/span&gt; (36 for 66 - &lt;em&gt;54.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;488.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-339)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$252,397.78&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.74 to 89.74 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 16 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;56.25%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 13 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;46.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
-    <t>rr</t>
+    <t>Chute Clock Foul</t>
+  </si>
+  <si>
+    <t>Chute  contact challenge; shawn ramirez; Successful challeange</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>.02 off 8 (granted auto challenge)</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>wow lots of rides in a row,shits on lucas theodoro the bull fighter who is hurt</t>
+  </si>
+  <si>
+    <t>Danny keep gets his 100th ride after 19 hour ride</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -986,6 +1004,28 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1008,7 +1048,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1020,6 +1060,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1359,6 +1402,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="17.1640625" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" style="9"/>
+    <col min="17" max="17" width="10.83203125" style="10"/>
+    <col min="18" max="18" width="10.83203125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
@@ -1407,13 +1453,13 @@
       <c r="O1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="S1" t="s">
@@ -1469,14 +1515,14 @@
       <c r="O2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="9">
         <v>43.1</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="10">
         <f>IF(OR(P2="",R2=""),0,R2-P2)</f>
         <v>45.35</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="11">
         <v>88.45</v>
       </c>
       <c r="T2" t="s">
@@ -1527,13 +1573,13 @@
       <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="9">
         <v>42.7</v>
       </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="11">
         <v>0</v>
       </c>
       <c r="T3" t="s">
@@ -1582,14 +1628,14 @@
       <c r="O4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="9">
         <v>41.7</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="10">
         <f t="shared" ref="Q3:Q44" ca="1" si="0">IF(OR(P4="",R4=""),0,R4-P4)</f>
         <v>45.4</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="11">
         <f ca="1">P4+Q4</f>
         <v>83.15</v>
       </c>
@@ -1639,13 +1685,13 @@
       <c r="O5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="9">
         <v>44.2</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="11">
         <v>0</v>
       </c>
       <c r="T5" t="s">
@@ -1694,13 +1740,13 @@
       <c r="O6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="9">
         <v>44.2</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
         <v>0</v>
       </c>
       <c r="T6" t="s">
@@ -1751,13 +1797,13 @@
       <c r="O7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="9">
         <v>41.1</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
+      <c r="Q7" s="10">
+        <v>83.85</v>
+      </c>
+      <c r="R7" s="11">
         <v>83.85</v>
       </c>
       <c r="T7" t="s">
@@ -1806,13 +1852,13 @@
       <c r="O8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="9">
         <v>44.15</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
         <f t="shared" ref="R8:R44" si="1">P8+Q8</f>
         <v>44.15</v>
       </c>
@@ -1864,13 +1910,13 @@
       <c r="O9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="9">
         <v>42.9</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
+      <c r="Q9" s="10">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
         <f t="shared" si="1"/>
         <v>42.9</v>
       </c>
@@ -1922,13 +1968,13 @@
       <c r="O10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
         <v>0</v>
       </c>
       <c r="T10" t="s">
@@ -1977,14 +2023,14 @@
       <c r="O11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="9">
         <v>43.55</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="10">
         <f t="shared" si="0"/>
         <v>45.960000000000008</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="11">
         <v>89.51</v>
       </c>
       <c r="T11" t="s">
@@ -2035,14 +2081,14 @@
       <c r="O12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P12" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>270</v>
-      </c>
-      <c r="R12" t="s">
-        <v>270</v>
+      <c r="P12" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>274</v>
       </c>
       <c r="T12" t="s">
         <v>19</v>
@@ -2094,14 +2140,14 @@
       <c r="O13" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="9">
         <v>43.15</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="10">
         <f t="shared" si="0"/>
         <v>43.000000000000007</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="11">
         <v>86.15</v>
       </c>
       <c r="T13" t="s">
@@ -2152,14 +2198,13 @@
       <c r="O14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="P14">
-        <v>43</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>-43</v>
-      </c>
-      <c r="R14">
+      <c r="P14" s="9">
+        <v>43.05</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>0</v>
+      </c>
+      <c r="R14" s="11">
         <v>0</v>
       </c>
       <c r="T14" t="s">
@@ -2210,15 +2255,15 @@
       <c r="O15" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
+      <c r="P15" s="9">
+        <v>42.5</v>
+      </c>
+      <c r="Q15" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
+        <v>45.5</v>
+      </c>
+      <c r="R15" s="11">
+        <v>88</v>
       </c>
       <c r="T15" t="s">
         <v>45</v>
@@ -2268,15 +2313,17 @@
       <c r="O16" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
+      <c r="P16" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="S16" t="s">
+        <v>270</v>
       </c>
       <c r="T16" t="s">
         <v>45</v>
@@ -2324,14 +2371,14 @@
       <c r="O17" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
+      <c r="P17" s="9">
+        <v>34.4</v>
+      </c>
+      <c r="Q17" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R17">
+        <v>-34.4</v>
+      </c>
+      <c r="R17" s="11">
         <v>0</v>
       </c>
       <c r="T17" t="s">
@@ -2382,14 +2429,14 @@
       <c r="O18" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
+      <c r="P18" s="9">
+        <v>43.85</v>
+      </c>
+      <c r="Q18" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R18">
+        <v>-43.85</v>
+      </c>
+      <c r="R18" s="11">
         <v>0</v>
       </c>
       <c r="T18" t="s">
@@ -2440,15 +2487,17 @@
       <c r="O19" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
+      <c r="P19" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="R19" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="S19" t="s">
+        <v>271</v>
       </c>
       <c r="T19" t="s">
         <v>38</v>
@@ -2496,14 +2545,14 @@
       <c r="O20" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
+      <c r="P20" s="9">
+        <v>43.1</v>
+      </c>
+      <c r="Q20" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R20">
+        <v>-43.1</v>
+      </c>
+      <c r="R20" s="11">
         <v>0</v>
       </c>
       <c r="T20" t="s">
@@ -2554,15 +2603,18 @@
       <c r="O21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
+      <c r="P21" s="9">
+        <v>42.85</v>
+      </c>
+      <c r="Q21" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
+        <v>42.15</v>
+      </c>
+      <c r="R21" s="11">
+        <v>85</v>
+      </c>
+      <c r="S21" t="s">
+        <v>273</v>
       </c>
       <c r="T21" t="s">
         <v>19</v>
@@ -2610,15 +2662,15 @@
       <c r="O22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
+      <c r="P22" s="9">
+        <v>42.8</v>
+      </c>
+      <c r="Q22" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
+        <v>45.5</v>
+      </c>
+      <c r="R22" s="11">
+        <v>88.3</v>
       </c>
       <c r="T22" t="s">
         <v>19</v>
@@ -2668,15 +2720,15 @@
       <c r="O23" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
+      <c r="P23" s="9">
+        <v>43.95</v>
+      </c>
+      <c r="Q23" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
+        <v>44.599999999999994</v>
+      </c>
+      <c r="R23" s="11">
+        <v>88.55</v>
       </c>
       <c r="T23" t="s">
         <v>19</v>
@@ -2726,15 +2778,18 @@
       <c r="O24" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
+      <c r="P24" s="9">
+        <v>41.25</v>
+      </c>
+      <c r="Q24" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
+        <v>43.25</v>
+      </c>
+      <c r="R24" s="11">
+        <v>84.5</v>
+      </c>
+      <c r="S24" t="s">
+        <v>275</v>
       </c>
       <c r="T24" t="s">
         <v>38</v>
@@ -2782,15 +2837,18 @@
       <c r="O25" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
+      <c r="P25" s="9">
+        <v>41.5</v>
+      </c>
+      <c r="Q25" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
+        <v>43.95</v>
+      </c>
+      <c r="R25" s="11">
+        <v>85.45</v>
+      </c>
+      <c r="S25" t="s">
+        <v>276</v>
       </c>
       <c r="T25" t="s">
         <v>45</v>
@@ -2842,14 +2900,14 @@
       <c r="O26" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
+      <c r="P26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="11">
         <v>0</v>
       </c>
       <c r="T26" t="s">
@@ -2900,14 +2958,14 @@
       <c r="O27" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
+      <c r="P27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="11">
         <v>0</v>
       </c>
       <c r="T27" t="s">
@@ -2958,14 +3016,14 @@
       <c r="O28" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
+      <c r="P28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="11">
         <v>0</v>
       </c>
       <c r="T28" t="s">
@@ -3016,14 +3074,14 @@
       <c r="O29" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
+      <c r="P29" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="11">
         <v>0</v>
       </c>
       <c r="T29" t="s">
@@ -3072,14 +3130,14 @@
       <c r="O30" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
+      <c r="P30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="11">
         <v>0</v>
       </c>
       <c r="T30" t="s">
@@ -3128,14 +3186,14 @@
       <c r="O31" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
+      <c r="P31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="11">
         <v>0</v>
       </c>
       <c r="T31" t="s">
@@ -3186,14 +3244,14 @@
       <c r="O32" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
+      <c r="P32" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="11">
         <v>0</v>
       </c>
       <c r="T32" t="s">
@@ -3246,14 +3304,14 @@
       <c r="O33" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
+      <c r="P33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="11">
         <v>0</v>
       </c>
       <c r="T33" t="s">
@@ -3304,14 +3362,14 @@
       <c r="O34" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
+      <c r="P34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="11">
         <v>0</v>
       </c>
       <c r="T34" t="s">
@@ -3362,14 +3420,14 @@
       <c r="O35" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
+      <c r="P35" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="11">
         <v>0</v>
       </c>
       <c r="T35" t="s">
@@ -3418,14 +3476,14 @@
       <c r="O36" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
+      <c r="P36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="11">
         <v>0</v>
       </c>
       <c r="T36" t="s">
@@ -3478,14 +3536,14 @@
       <c r="O37" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
+      <c r="P37" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="11">
         <v>0</v>
       </c>
       <c r="T37" t="s">
@@ -3536,14 +3594,14 @@
       <c r="O38" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
+      <c r="P38" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="11">
         <v>0</v>
       </c>
       <c r="T38" t="s">
@@ -3596,14 +3654,14 @@
       <c r="O39" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
+      <c r="P39" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="11">
         <v>0</v>
       </c>
       <c r="T39" t="s">
@@ -3652,14 +3710,14 @@
       <c r="O40" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
+      <c r="P40" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="11">
         <v>0</v>
       </c>
       <c r="T40" t="s">
@@ -3712,14 +3770,14 @@
       <c r="O41" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
+      <c r="P41" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="11">
         <v>0</v>
       </c>
       <c r="T41" t="s">
@@ -3770,14 +3828,14 @@
       <c r="O42" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
+      <c r="P42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="11">
         <v>0</v>
       </c>
       <c r="T42" t="s">
@@ -3828,14 +3886,14 @@
       <c r="O43" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
+      <c r="P43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="11">
         <v>0</v>
       </c>
       <c r="T43" t="s">
@@ -3888,14 +3946,14 @@
       <c r="O44" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
+      <c r="P44" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="11">
         <v>0</v>
       </c>
       <c r="T44" t="s">
@@ -3949,5 +4007,6 @@
     <hyperlink ref="J44" r:id="rId43" display="https://probullstats.com/loggers/matchup.php?bull=54035&amp;guy=Dalton+Kasel" xr:uid="{0EDD66C9-F792-EC45-A24C-1F3BD6F40636}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>